--- a/601998_CNCB/601998_CNCB.xlsx
+++ b/601998_CNCB/601998_CNCB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\18803\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\PythonProject\A-share-Bank-Financial-Report-Analysis\601998_CNCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4F8052-CAD1-4470-B36F-F2A1A9E58497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B74E291-1413-4DA4-B86A-7F63099D6078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6540" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="35">
   <si>
     <t>营业收入</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -48,10 +48,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每股现金流净额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>平均资产收益率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -160,18 +156,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>人民币流动性比例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>外币流动性比例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>流动性覆盖率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>正常类贷款迁徙率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -185,10 +169,6 @@
   </si>
   <si>
     <t>可疑类贷款迁徙率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>经现流</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -537,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -563,305 +543,265 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>443082</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.19</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>7.96</v>
+        <v>9.2799999999999994</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>0.73</v>
+        <v>10131028</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>9.2799999999999994</v>
+        <v>5862172</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>10131028</v>
+        <v>67216</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>5862172</v>
+        <v>136856</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>67216</v>
+        <v>9283398</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>136856</v>
+        <v>2069377</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>9283398</v>
+        <v>2185649</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>2069377</v>
+        <v>473380</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>2185649</v>
+        <v>1320869</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>473380</v>
+        <v>723865</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>1320869</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>723865</v>
+        <v>983968</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>13.01</v>
+        <v>728608</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>983968</v>
+        <v>7684339</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>728608</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>7684339</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>1.6</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>1.63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>68</v>
+        <v>31.61</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>32</v>
+        <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>31.61</v>
+        <v>203.61</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>1.1499999999999999</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>203.61</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>0.89</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>9.48</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>10.9</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>12.8</v>
+        <v>29.37</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>68.47</v>
+        <v>61.36</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>62.28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>144.22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>29.37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>61.36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>54.61</v>
       </c>
     </row>
@@ -873,7 +813,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95170128-8B75-4B3C-B904-1E83CD2631DB}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -898,305 +838,265 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>-181032</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.19</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>-3.33</v>
+        <v>9.7100000000000009</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>0.75</v>
+        <v>9532722</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>9.7100000000000009</v>
+        <v>5720128</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>9532722</v>
+        <v>66485</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>5720128</v>
+        <v>139240</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>66485</v>
+        <v>8725357</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>139240</v>
+        <v>2054271</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>8725357</v>
+        <v>2062315</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>2054271</v>
+        <v>439965</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>2062315</v>
+        <v>1221680</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>439965</v>
+        <v>684316</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>1221680</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>684316</v>
+        <v>944160</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>12.58</v>
+        <v>687134</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>944160</v>
+        <v>7068736</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>687134</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>7068736</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>1.71</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>1.77</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>68.7</v>
+        <v>32.49</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>31.3</v>
+        <v>1.1599999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>32.49</v>
+        <v>209.43</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>1.1599999999999999</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>209.43</v>
+        <v>9.7200000000000006</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>0.95</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>9.7200000000000006</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>11.26</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>13.36</v>
+        <v>26.44</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>73.47</v>
+        <v>63.28</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>67.23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>218.13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>26.44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>63.28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>73.88</v>
       </c>
     </row>
@@ -1208,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85425F0F-59CE-4DB1-AEFB-6317792C8147}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -1233,305 +1133,265 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>-918</v>
+        <v>1.1399999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.1399999999999999</v>
+        <v>1.1299999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.1299999999999999</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>-0.02</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>0.77</v>
+        <v>9052484</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>10.71</v>
+        <v>5498344</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>9052484</v>
+        <v>64800</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>5498344</v>
+        <v>134517</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>64800</v>
+        <v>8317809</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>134517</v>
+        <v>2187273</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>8317809</v>
+        <v>1745094</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>2187273</v>
+        <v>340432</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1745094</v>
+        <v>1125384</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>340432</v>
+        <v>602281</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>1125384</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>602281</v>
+        <v>869853</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>12.3</v>
+        <v>605156</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>869853</v>
+        <v>6727713</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>605156</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>6727713</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>1.75</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>1.78</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>69.7</v>
+        <v>32.35</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>30.3</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>32.35</v>
+        <v>207.59</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>1.18</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>207.59</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>0.93</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>8.99</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>10.75</v>
+        <v>2.1800000000000002</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>12.93</v>
+        <v>36.700000000000003</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>52</v>
+        <v>83.18</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>64.83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>167.48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>2.1800000000000002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>36.700000000000003</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>83.18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>88.83</v>
       </c>
     </row>
@@ -1543,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C7E03-EEF9-4665-8CD6-6DD93ACE52AD}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -1568,305 +1428,265 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>195066</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.05</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>3.99</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>0.76</v>
+        <v>8547543</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>10.75</v>
+        <v>5152772</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>8547543</v>
+        <v>65213</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>5152772</v>
+        <v>131202</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>65213</v>
+        <v>7861713</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>131202</v>
+        <v>1951555</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>7861713</v>
+        <v>1855977</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>1951555</v>
+        <v>349013</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1855977</v>
+        <v>942803</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>349013</v>
+        <v>550477</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>942803</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>550477</v>
+        <v>832087</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>11.25</v>
+        <v>551863</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>832087</v>
+        <v>6315506</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>551863</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>6315506</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>1.92</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>1.97</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>71.3</v>
+        <v>30.53</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>28.7</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>30.53</v>
+        <v>201.19</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>1.27</v>
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>201.19</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>1.1200000000000001</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>8.74</v>
+        <v>13.18</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>10.63</v>
+        <v>2.2599999999999998</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>13.18</v>
+        <v>29.38</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>62.18</v>
+        <v>73.430000000000007</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>69.239999999999995</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>168.03</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>2.2599999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>29.38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>73.430000000000007</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>78.75</v>
       </c>
     </row>
@@ -1878,7 +1698,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC5A80D1-36BE-41ED-8116-E82E59B3F5CA}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -1903,305 +1723,265 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>-75394</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>0.97</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>-1.54</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>0.72</v>
+        <v>8042884</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>10.7</v>
+        <v>4855969</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>8042884</v>
+        <v>67459</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>4855969</v>
+        <v>121471</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>67459</v>
+        <v>7400258</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>121471</v>
+        <v>1974319</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>7400258</v>
+        <v>1789956</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>1974319</v>
+        <v>310054</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1789956</v>
+        <v>662255</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>310054</v>
+        <v>511362</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>662255</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>511362</v>
+        <v>785811</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>10.45</v>
+        <v>514078</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>785811</v>
+        <v>5809523</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>514078</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>5809523</v>
+        <v>2.0499999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>1.99</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>2.0499999999999998</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>72.3</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>27.7</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>29.2</v>
+        <v>180.07</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>1.39</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>180.07</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>1.08</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>8.85</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>10.88</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>13.53</v>
+        <v>32.869999999999997</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>59.99</v>
+        <v>77.19</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>58.98</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>146.59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>32.869999999999997</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>77.19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>58.93</v>
       </c>
     </row>
@@ -2213,7 +1993,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788DE462-357D-41E8-8E9A-DAF92235A9EE}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -2238,15 +2018,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>156863</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
         <v>0.86</v>
@@ -2254,191 +2034,191 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>0.86</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>3.21</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>0.69</v>
+        <v>7511161</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>10.07</v>
+        <v>4473307</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>7511161</v>
+        <v>73452</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>4473307</v>
+        <v>126100</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>73452</v>
+        <v>6951123</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>126100</v>
+        <v>1915266</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>6951123</v>
+        <v>1674846</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>1915266</v>
+        <v>327110</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1674846</v>
+        <v>611177</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>327110</v>
+        <v>469625</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>611177</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>469625</v>
+        <v>701729</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>9.6</v>
+        <v>471251</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>701729</v>
+        <v>5393248</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>471251</v>
+        <v>2.1800000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>5393248</v>
+        <v>2.2599999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>2.1800000000000002</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>2.2599999999999998</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>77.3</v>
+        <v>26.65</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>22.7</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>26.65</v>
+        <v>171.68</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
         <v>1.64</v>
@@ -2446,97 +2226,57 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>171.68</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>1.64</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>8.74</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>10.18</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>13.01</v>
+        <v>48.12</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>58.04</v>
+        <v>76.819999999999993</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>71.56</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>135.13999999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>3.52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>48.12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>76.819999999999993</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>70.34</v>
       </c>
     </row>
